--- a/Test_data/New_Architecture/Complex_Scenario/Marks_Poor.xlsx
+++ b/Test_data/New_Architecture/Complex_Scenario/Marks_Poor.xlsx
@@ -447,10 +447,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -460,10 +460,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -499,10 +499,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -512,10 +512,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -525,10 +525,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -590,10 +590,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -629,10 +629,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>2</v>
@@ -655,10 +655,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -681,10 +681,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -694,10 +694,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -733,10 +733,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1040,7 +1040,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
         <v>2</v>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1235,7 +1235,7 @@
         <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1970,10 +1970,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2248,10 +2248,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
         <v>2</v>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2433,7 +2433,7 @@
         <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>2</v>
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2996,19 +2996,19 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3018,22 +3018,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -3043,22 +3043,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3068,22 +3068,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3093,19 +3093,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
@@ -3118,22 +3118,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -3168,22 +3168,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -3193,22 +3193,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -3218,22 +3218,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -3243,22 +3243,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -3268,22 +3268,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3293,22 +3293,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -3318,22 +3318,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -3343,22 +3343,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -3368,22 +3368,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -3393,22 +3393,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -3418,22 +3418,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -3443,22 +3443,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3468,22 +3468,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -3493,22 +3493,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -3518,22 +3518,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -3543,22 +3543,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="n">
         <v>4</v>
       </c>
-      <c r="D24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1.4</v>
-      </c>
       <c r="G24" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -3568,22 +3568,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3593,22 +3593,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -3618,22 +3618,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -3643,22 +3643,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -3668,22 +3668,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -3693,22 +3693,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -3718,22 +3718,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3794,22 +3794,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3819,22 +3819,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3844,22 +3844,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3869,19 +3869,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -3894,22 +3894,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3919,22 +3919,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3944,22 +3944,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3969,22 +3969,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3994,22 +3994,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4019,22 +4019,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4044,22 +4044,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4069,22 +4069,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -4094,22 +4094,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -4119,22 +4119,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4144,22 +4144,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -4169,22 +4169,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -4194,22 +4194,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -4219,22 +4219,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -4244,22 +4244,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -4272,19 +4272,19 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -4294,22 +4294,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -4319,19 +4319,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -4344,22 +4344,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -4369,22 +4369,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -4397,19 +4397,19 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -4419,22 +4419,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -4444,22 +4444,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -4469,22 +4469,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -4494,22 +4494,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -4519,22 +4519,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Test_data/New_Architecture/Complex_Scenario/Marks_Poor.xlsx
+++ b/Test_data/New_Architecture/Complex_Scenario/Marks_Poor.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -489,7 +489,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -512,10 +512,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -593,7 +593,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>2</v>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>2</v>
@@ -694,10 +694,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
         <v>2</v>
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -775,7 +775,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>2</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -814,7 +814,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -910,7 +910,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1066,7 +1066,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>2</v>
@@ -1196,7 +1196,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1318,7 +1318,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1344,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1435,7 +1435,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>2</v>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
         <v>2</v>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
         <v>2</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1526,7 +1526,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1539,7 +1539,7 @@
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1591,7 +1591,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1604,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
         <v>2</v>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1669,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1765,7 +1765,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1778,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -1817,7 +1817,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>2</v>
@@ -1869,7 +1869,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1921,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1934,7 +1934,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1973,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
         <v>2</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2064,7 +2064,7 @@
         <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2077,7 +2077,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
         <v>2</v>
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>2</v>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2212,7 +2212,7 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2290,7 +2290,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2303,7 +2303,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -2316,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2394,7 +2394,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2407,7 +2407,7 @@
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -2459,7 +2459,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2485,7 +2485,7 @@
         <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2555,7 +2555,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -2620,7 +2620,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>2</v>
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>2</v>
@@ -2750,7 +2750,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -2786,10 +2786,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -2815,7 +2815,7 @@
         <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -2828,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
@@ -2867,7 +2867,7 @@
         <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2880,7 +2880,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2919,7 +2919,7 @@
         <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2993,22 +2993,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -3021,19 +3021,19 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -3043,22 +3043,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -3068,22 +3068,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3093,22 +3093,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3118,22 +3118,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
         <v>5</v>
       </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -3168,22 +3168,22 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
         <v>4</v>
       </c>
-      <c r="C9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>3</v>
       </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -3193,22 +3193,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>4</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -3218,13 +3218,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>4</v>
@@ -3233,7 +3233,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -3243,22 +3243,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -3268,22 +3268,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
         <v>3</v>
       </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -3293,22 +3293,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -3318,22 +3318,22 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="n">
         <v>3</v>
       </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
       <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
         <v>5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
         <v>4</v>
@@ -3355,7 +3355,7 @@
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
@@ -3368,22 +3368,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -3393,22 +3393,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -3418,22 +3418,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -3443,22 +3443,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -3468,22 +3468,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -3493,22 +3493,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -3521,13 +3521,13 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
         <v>4</v>
       </c>
-      <c r="D23" t="n">
-        <v>3</v>
-      </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
         <v>3</v>
@@ -3543,19 +3543,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
         <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
         <v>3</v>
@@ -3568,22 +3568,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -3593,22 +3593,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
         <v>3</v>
       </c>
-      <c r="D26" t="n">
-        <v>4</v>
-      </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -3618,22 +3618,22 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="n">
         <v>5</v>
       </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
@@ -3652,13 +3652,13 @@
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -3668,19 +3668,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -3693,19 +3693,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="n">
         <v>5</v>
       </c>
-      <c r="D30" t="n">
-        <v>2</v>
-      </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -3718,19 +3718,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -3797,16 +3797,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -3822,10 +3822,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3847,7 +3847,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -3856,7 +3856,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -3869,13 +3869,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3894,16 +3894,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -3931,10 +3931,10 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -3947,13 +3947,13 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -3978,13 +3978,13 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4003,13 +4003,13 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -4047,13 +4047,13 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -4069,19 +4069,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -4100,16 +4100,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -4153,13 +4153,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -4169,13 +4169,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -4197,7 +4197,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
@@ -4206,10 +4206,10 @@
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -4222,16 +4222,16 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -4244,16 +4244,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -4272,16 +4272,16 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -4294,16 +4294,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -4331,10 +4331,10 @@
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
@@ -4359,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -4381,7 +4381,7 @@
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -4397,7 +4397,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
@@ -4406,7 +4406,7 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -4444,16 +4444,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -4478,7 +4478,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
@@ -4497,19 +4497,19 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -4522,19 +4522,19 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
